--- a/out/test_recursed.xlsx
+++ b/out/test_recursed.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,16 @@
           <t>Код (6,2)</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Code (4,2)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Code (5,2)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,6 +482,12 @@
       <c r="E2" t="n">
         <v>85</v>
       </c>
+      <c r="F2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -488,6 +504,12 @@
       <c r="E3" t="n">
         <v>58</v>
       </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -501,6 +523,9 @@
       <c r="E4" t="n">
         <v>33</v>
       </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -513,6 +538,9 @@
       </c>
       <c r="E5" t="n">
         <v>18</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
